--- a/tests/workbooktests/workbooks/test_futures.xlsx
+++ b/tests/workbooktests/workbooks/test_futures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D86665A-8818-4374-BA74-2C3B1D9F6338}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EADCB26-608E-48D1-AB5E-E45C8B35CEC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3885" yWindow="-18240" windowWidth="30690" windowHeight="16530" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
   </bookViews>
@@ -996,11 +996,11 @@
         <v>18</v>
       </c>
       <c r="B10" s="21" t="str">
-        <f>_xll.qlFlatForward(B1,0.03,,"Continuous")</f>
+        <f>_xll.qlFlatForward(B1,0.03,"actual365fixed","Continuous")</f>
         <v>欣[test_futures.xlsx]PerpetualFutures!R10C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C10" s="21" t="str">
-        <f>_xll.qlFlatForward(B1,0.03,,"Continuous")</f>
+        <f>_xll.qlFlatForward(B1,0.03,"actual365fixed","Continuous")</f>
         <v>欣[test_futures.xlsx]PerpetualFutures!R10C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1009,11 +1009,11 @@
         <v>19</v>
       </c>
       <c r="B11" s="21" t="str">
-        <f>_xll.qlFlatForward(B1,0.03,,"Continuous")</f>
+        <f>_xll.qlFlatForward(B1,0.03,"actual365fixed","Continuous")</f>
         <v>欣[test_futures.xlsx]PerpetualFutures!R11C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C11" s="21" t="str">
-        <f>_xll.qlFlatForward(B1,0.03,,"Continuous")</f>
+        <f>_xll.qlFlatForward(B1,0.03,"actual365fixed","Continuous")</f>
         <v>欣[test_futures.xlsx]PerpetualFutures!R11C3YieldTermStructureHandle,A</v>
       </c>
     </row>
